--- a/Data_Science_AI_Final_Exhaustive_Syllabus (1).xlsx
+++ b/Data_Science_AI_Final_Exhaustive_Syllabus (1).xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mathematics &amp; Stats" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python &amp; Core Libraries" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power BI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machine Learning" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reinforcement Learning" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deep Learning Architectures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generative AI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Data Infrastructure" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python &amp; Core Libraries" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power BI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machine Learning" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reinforcement Learning" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deep Learning Architectures" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generative AI" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -528,8 +529,8 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -582,7 +583,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Day 01</t>
@@ -600,7 +601,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Vector configurations, magnitude, additions, scalar dot products, vector cosine similarity spaces</t>
+          <t>Vector space dimensions, additions, inner scalar dot products, distance metrics, coordinate geometry</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -610,7 +611,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Implement a vector similarity score comparison script manually using pure Python loops</t>
+          <t>Code custom array operations to measure vector-wise similarity matrices manually</t>
         </is>
       </c>
       <c r="G4" s="6">
@@ -622,7 +623,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Day 02</t>
@@ -662,7 +663,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Day 03</t>
@@ -702,7 +703,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Day 04</t>
@@ -742,7 +743,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Day 05</t>
@@ -782,7 +783,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Day 06</t>
@@ -822,7 +823,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Day 07</t>
@@ -862,7 +863,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Day 08</t>
@@ -902,7 +903,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Day 09</t>
@@ -942,7 +943,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Day 10</t>
@@ -982,7 +983,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Day 11</t>
@@ -1022,7 +1023,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Day 12</t>
@@ -1062,7 +1063,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Day 13</t>
@@ -1102,7 +1103,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Day 14</t>
@@ -1156,23 +1157,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Exhaustive Python Foundations, OOP, NumPy Core, Pandas Wrangling, Matplotlib Plots &amp; Scikit-Learn Pipelines (Days 15 - 39)</t>
+          <t>Relational Database Infrastructure &amp; Extended SQL Queries (Days 15 - 21)</t>
         </is>
       </c>
     </row>
@@ -1190,22 +1191,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Topic / Library</t>
+          <t>Topic Title</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Detailed Concepts &amp; Class Architectures</t>
+          <t>Detailed Query Concepts &amp; Syntax Chains</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Purpose (Why Learn This?)</t>
+          <t>Purpose (Why Learn This Concept?)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Daily Coding Objective / Milestone</t>
+          <t>Hands-On Practical Database Target</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1219,7 +1220,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Day 15</t>
@@ -1232,34 +1233,34 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Python Core: Basics</t>
+          <t>SQL Foundations: Ingestion &amp; SELECT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Anaconda setup, virtual environments (venv), dynamic variable variables, primitives (int, float, string, boolean)</t>
+          <t>RDBMS database setup scripts, relational mapping constraints, primitive types, primary keys vs foreign keys, SELECT statements, WHERE conditional constraints, LIMIT syntax modifications</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>To build a functional data science runtime terminal and grasp native primitive data objects.</t>
+          <t>To hook up local query systems to relational data servers and extract target data column vectors safely.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Provision workspace; write an automated module executing standard variable assignments</t>
+          <t>Install PostgreSQL, configure database access rules, and run targeted scripts to query row subsets cleanly</t>
         </is>
       </c>
       <c r="G4" s="6">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/index.html", "Official Docs")</f>
+        <f>HYPERLINK("https://www.w3schools.com/sql/", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=kqtD5eraYLY", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Day 16</t>
@@ -1272,34 +1273,34 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Python Core: Flow Control</t>
+          <t>SQL: Logical Filtering &amp; wildcards</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Conditional evaluation testing (if, elif, else), logical verification parameters, matching filters</t>
+          <t>Compound logic chaining parameters (AND, OR, NOT), localized range screening (IN, BETWEEN), descriptive string filtering via LIKE and wildcards tokens</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>To direct data workflows and validation filters cleanly using conditional expressions.</t>
+          <t>To find or filter specific user profiles or order cohorts meeting strict, multi-layer parameters.</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Code a multi-tier customer validation program parsing relational parameters</t>
+          <t>Query consumer table matrices to isolate subset groups using conditional pattern checks across values</t>
         </is>
       </c>
       <c r="G5" s="10">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html", "Official Docs")</f>
+        <f>HYPERLINK("https://www.w3schools.com/sql/sql_operators.asp", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H5" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DZwmZ8yC7xk", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Day 17</t>
@@ -1312,34 +1313,34 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Python Core: Iterations</t>
+          <t>SQL: Column Aggregations &amp; Groupings</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>for statements, while conditions, loop step routing keywords (break, continue)</t>
+          <t>Data aggregators operations (COUNT, SUM, AVG, MIN, MAX), spatial table partitioning via GROUP BY, post-aggregation bucket filtering using HAVING statement boundaries</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>To automatically parse large external text lines and index logs without manual intervention.</t>
+          <t>To compute aggregate variables like total corporate revenue performance indicators or categorical benchmarks.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Develop an interactive check system utilizing conditional while-loop structures</t>
+          <t>Formulate aggregate partition rows summarizing financial order counts grouped across region attributes</t>
         </is>
       </c>
       <c r="G6" s="6">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html#for-statements", "Official Docs")</f>
+        <f>HYPERLINK("https://www.w3schools.com/sql/sql_groupby.asp", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H6" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6iF8Xb7Z3wQ", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Day 18</t>
@@ -1352,34 +1353,34 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Python Core: Collections 1</t>
+          <t>SQL: Relational Multi-Table Joins</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>List indices, slicing paths, list mutations, tuple constraints, List Comprehensions</t>
+          <t>Database normalization principles, table schema alignment loops, cross-referencing fields using INNER JOIN and LEFT JOIN structures</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>To arrange array collections, tracking coordinate data lines via mapping compressions.</t>
+          <t>To stitch separate normalized relational tables together smoothly into comprehensive analytical datasets.</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Process tabular rows saved inside nested lists using compression paths</t>
+          <t>Combine live order row elements directly onto corresponding user profile demographic indices completely</t>
         </is>
       </c>
       <c r="G7" s="10">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/datastructures.html", "Official Docs")</f>
+        <f>HYPERLINK("https://www.w3schools.com/sql/sql_join.asp", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H7" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W8KRzm-HUcc", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Day 19</t>
@@ -1392,34 +1393,34 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Python Core: Collections 2</t>
+          <t>SQL: Advanced Outer &amp; Self Joins</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Key-value pair dictionaries, lookup hashing mechanics, unique sets, set metrics</t>
+          <t>RIGHT JOIN boundary rules, FULL OUTER JOIN conditions, matching table records back onto themselves natively (Self-Joins)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>To deploy high-speed lookup tables and track unique target categories rapidly.</t>
+          <t>To examine relational gaps across databases and map hierarchical tree chart variables.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Write a word-frequency scanner checking raw document files for terms</t>
+          <t>Construct a hierarchical self-join query mapping corporate structure tables linking employees to manager IDs</t>
         </is>
       </c>
       <c r="G8" s="6">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/datastructures.html#dictionaries", "Official Docs")</f>
+        <f>HYPERLINK("https://www.w3schools.com/sql/sql_join_full.asp", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H8" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=daefaLgNkw0", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Day 20</t>
@@ -1432,34 +1433,34 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Python Core: Functions</t>
+          <t>SQL: Subqueries &amp; Partition Windows</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>def statement parameters, return tracks, positional arguments, keyword unpacking (*args, **kwargs)</t>
+          <t>Nested subqueries loops, sub-select configurations, statement optimization, partition window functions (ROW_NUMBER, RANK, DENSE_RANK counters)</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>To bundle messy code paths into cleanly organized, reusable functional building blocks.</t>
+          <t>To calculate granular, row-level metrics relative to their specific category partition averages.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Encapsulate loose collection code blocks into modular reusable functions</t>
+          <t>Rank transaction entries within product rows without losing the granularity of raw lines</t>
         </is>
       </c>
       <c r="G9" s="10">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html#defining-functions", "Official Docs")</f>
+        <f>HYPERLINK("https://mode.com/sql-tutorial/sql-subqueries/", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H9" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9Os0o3wXykM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HXV3zeQKqGY", "Watch Video Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Day 21</t>
@@ -1472,750 +1473,30 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Project: Ingestion Script</t>
+          <t>Project: Advanced SQL Architecture</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>File reading strings natively, context managers (with open), text string modifications, JSON parsing</t>
+          <t>Common Table Expressions (CTEs), syntax loops, complex multi-join optimization passes</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>To join native data structures, building functional file parsing scripts from scratch.</t>
+          <t>To combine advanced extraction features into single production-ready database scripts.</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Project: Code a CLI-driven Retail System saving records dynamically via context blocks</t>
+          <t>Project: Query Complex E-Commerce System to Calculate Monthly User Cohort Retentions via CTEs</t>
         </is>
       </c>
       <c r="G10" s="6">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/inputoutput.html#reading-and-writing-files", "Official Docs")</f>
+        <f>HYPERLINK("https://mode.com/sql-tutorial/sql-window-functions/", "Official Docs Reference")</f>
         <v/>
       </c>
       <c r="H10" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Uh2ebFW8OYM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Day 22</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Python OOP: Classes</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Class blueprints instantiation, instance variables, methods, constructors (__init__), namespaces</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>To group structured methods and state variables into reusable object blueprints.</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Model core corporate elements (e.g. Employee data card structures) using objects</t>
-        </is>
-      </c>
-      <c r="G11" s="10">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/classes.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZDa-Z5JzLYM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Day 23</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Python OOP: Inheritance</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Hierarchical inheritance, sub-classes expansion, function polymorphism, custom method overrides</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>To establish flexible, hierarchical system dependencies without code duplication.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Extend functional class layers into advanced sub-category objects overriding method calls</t>
-        </is>
-      </c>
-      <c r="G12" s="6">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/classes.html#inheritance", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RSl87lqOXDE", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Day 24</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Python OOP: Advanced Logic</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Private attributes (__), property getters/setters, try-except-finally blocks, custom errors</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>To implement defensive exception containment rules protecting critical module data metrics.</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Enforce strict input verification masks using private properties and exception catch blocks</t>
-        </is>
-      </c>
-      <c r="G13" s="10">
-        <f>HYPERLINK("https://docs.python.org/3/tutorial/errors.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=apACNr7YdyE", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Day 25</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Ecosystem Layer: NumPy 1</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>ND-arrays properties, vector types, initializing elements (zeros, ones, arange), slicing coordinates</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>To replace loop operations with high-speed vectorized computation blocks.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Initialize multi-dimensional arrays, slicing target internal matrix sub-regions</t>
-        </is>
-      </c>
-      <c r="G14" s="6">
-        <f>HYPERLINK("https://numpy.org/doc/stable/user/absolute_beginners.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H14" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Day 26</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Ecosystem Layer: NumPy 2</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Vector math rules, universal functions (ufuncs), axis aggregate statistics, shape transformations</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>To execute algebraic adjustments across extensive multi-axis grids instantly.</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Flatten complex multi-dimensional visual input channel blocks down to linear feature frames</t>
-        </is>
-      </c>
-      <c r="G15" s="10">
-        <f>HYPERLINK("https://numpy.org/doc/stable/reference/ufuncs.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Day 27</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Ecosystem Layer: NumPy 3</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Matrix broadcasting alignments, boolean masking logic filters, index arrays extraction</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>To filter numerical rows instantly using spatial boolean mask matrices.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Extract numerical vector values from record lines exceeding standard outliers via boolean filters</t>
-        </is>
-      </c>
-      <c r="G16" s="6">
-        <f>HYPERLINK("https://numpy.org/doc/stable/user/basics.broadcasting.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H16" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Wrangling Layer: Pandas 1</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Series attributes, DataFrame layouts, ingestion connectors (read_csv, read_excel, read_json)</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>To manage storage inputs as queryable tabular layers programmatically.</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Load coarse raw data frames, isolating target coordinate rows via boolean masks</t>
-        </is>
-      </c>
-      <c r="G17" s="10">
-        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/dsintro.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Day 29</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Wrangling Layer: Pandas 2</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Explicit index locators (loc/iloc), compound query masks, sorting parameters labels</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>To isolate data partitions using exact coordinate axis labels safely.</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Filter customer dataset rows matching multiple custom financial threshold ranges</t>
-        </is>
-      </c>
-      <c r="G18" s="6">
-        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/indexing.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H18" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Day 30</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Wrangling Layer: Pandas 3</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Missing data tracks (isnull), data imputations via fillna, deleting observations (dropna)</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>To handle missing data blocks cleanly using statistical column median rules.</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Construct an automated cleansing pipe replacing missing cells with column median values</t>
-        </is>
-      </c>
-      <c r="G19" s="10">
-        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/missing_data.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Day 31</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Wrangling Layer: Pandas 4</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Feature engineering, element-wise transformations (.apply), column splitting, mapping strings</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>To map continuous feature columns and extract components from unstructured categories.</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Convert continuous transaction columns into categorized string feature groups dynamically</t>
-        </is>
-      </c>
-      <c r="G20" s="6">
-        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/basics.html#function-application", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H20" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Day 32</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Wrangling Layer: Pandas 5</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Splitting segments via groupby, multi-aggregations (.agg), multi-key table lookups via merge</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>To connect separate transactional tables and group data points into segment metrics.</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Combine customer support interaction log frames with transactional record fields</t>
-        </is>
-      </c>
-      <c r="G21" s="10">
-        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/groupby.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Day 33</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Visualization: Matplotlib</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Figure canvas layouts, axis properties formatting, titles, labels, legends customization, grids</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>To build polished graphical representations conveying key data features clearly.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Format active chart components using explicit font styles, legend bounds, and hex colors</t>
-        </is>
-      </c>
-      <c r="G22" s="6">
-        <f>HYPERLINK("https://matplotlib.org/stable/users/explain/quick_start.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H22" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Day 34</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Visualization: Diagnostics</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Histograms bins setups, box plots distributions, scatter plots with alpha transparency parameter settings</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>To spot statistical variations, spatial correlations, and outliers visually.</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Graph product distribution ranges to inspect feature data variations and catch outliers</t>
-        </is>
-      </c>
-      <c r="G23" s="10">
-        <f>HYPERLINK("https://matplotlib.org/stable/api/_as_gen/matplotlib.pyplot.hist.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H23" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Day 35</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Visualization: Panels &amp; Grids</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Multi-panel subplots creation (plt.subplots), axis coordinates routing, exporting graphics (savefig)</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>To bundle separate metrics into uniform scientific report layouts cleanly.</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Construct unified multi-chart dashboard views showing lines, bars, and boxes side-by-side</t>
-        </is>
-      </c>
-      <c r="G24" s="6">
-        <f>HYPERLINK("https://matplotlib.org/stable/gallery/subplots_axes_and_figures/subplots_demo.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H24" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Day 36</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Scikit-Learn Preprocessing</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Data split partitions (train_test_split), categorical encoding mappings, standard data scaling</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>To partition metrics arrays and scale independent features uniformly before running modeling.</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Pass unpolished string features through robust preprocessing pipelines utilizing automated scaling arrays</t>
-        </is>
-      </c>
-      <c r="G25" s="10">
-        <f>HYPERLINK("https://scikit-learn.org/stable/modules/preprocessing.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H25" s="10">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLblh5JKOoLUICTaGLRoHQDuF_7q2GfuJF", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Day 37</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Scikit-Learn Estimation</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Supervised Ordinary Least Squares (LinearRegression), matching fit indices, checking model attributes</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>To compute continuous linear parameters and trace parameter correlation indicators.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Build and fit a predictive regression model tracking feature correlations to metric outputs</t>
-        </is>
-      </c>
-      <c r="G26" s="6">
-        <f>HYPERLINK("https://scikit-learn.org/stable/modules/linear_model.html#ordinary-least-squares", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H26" s="6">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLblh5JKOoLUICTaGLRoHQDuF_7q2GfuJF", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Day 38</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Scikit-Learn Verification</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Loss scoring calculators (mean_absolute_error, mean_squared_error, r2_score variance metric boundaries)</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>To verify model predictive drop thresholds against test subsets.</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Compute continuous validation errors testing models against separate check files</t>
-        </is>
-      </c>
-      <c r="G27" s="10">
-        <f>HYPERLINK("https://scikit-learn.org/stable/modules/model_evaluation.html#regression-metrics", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H27" s="10">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLKnIA16_RmvbAl7lyqVvRI-cz3BwAd3mU", "Watch Tutorial Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Day 39</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Project: Pipeline Release</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Pipeline blocks assembly, grid parameter hyperparameter tuning loops via GridSearchCV arrays via Git</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>To build and track complete data-prep to model-inference flows via Git.</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>Project: Develop OOP Data Processing, Cleaning &amp; Visual Reporting Engine via Git Workflow</t>
-        </is>
-      </c>
-      <c r="G28" s="6">
-        <f>HYPERLINK("https://scikit-learn.org/stable/modules/generated/sklearn.pipeline.Pipeline.html", "Official Docs")</f>
-        <v/>
-      </c>
-      <c r="H28" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0B5eIE_1vpU", "Watch Tutorial Course")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=w7viXg6bFwU", "Watch Video Course")</f>
         <v/>
       </c>
     </row>
@@ -2233,6 +1514,1083 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exhaustive Python Foundations, OOP, NumPy Core, Pandas Wrangling, Matplotlib Plots &amp; Scikit-Learn Pipelines (Days 22 - 46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Topic / Library</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Concepts &amp; Class Architectures</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Purpose (Why Learn This?)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Daily Coding Objective / Milestone</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Documentation Link</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>YouTube Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Python Core Basics</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Anaconda setup, virtual environments (venv), dynamic variable variables, primitives (int, float, string, boolean)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>To build a functional data science runtime terminal and grasp native primitive data objects.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Provision workspace; write an automated module executing standard variable assignments</t>
+        </is>
+      </c>
+      <c r="G4" s="6">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/index.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=kqtD5eraYLY", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Python Flow Controls</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Conditional evaluation testing (if, elif, else), logical verification parameters, matching filters</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>To direct data workflows and validation filters cleanly using conditional expressions.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Code a multi-tier customer validation program parsing relational parameters</t>
+        </is>
+      </c>
+      <c r="G5" s="10">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DZwmZ8yC7xk", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Python Loops Engine</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>for statements, while conditions, loop step routing keywords (break, continue)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>To automatically parse large external text lines and index logs without manual intervention.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Develop an interactive check system utilizing conditional while-loop structures</t>
+        </is>
+      </c>
+      <c r="G6" s="6">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html#for-statements", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6iF8Xb7Z3wQ", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Python Collections 1</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>List indices, slicing paths, list mutations, tuple constraints, List Comprehensions</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>To arrange array collections, tracking coordinate data lines via mapping compressions.</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Process tabular rows saved inside nested lists using compression paths</t>
+        </is>
+      </c>
+      <c r="G7" s="10">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/datastructures.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W8KRzm-HUcc", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Python Collections 2</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Key-value pair dictionaries, lookup hashing mechanics, unique sets, set metrics</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>To deploy high-speed lookup tables and track unique target categories rapidly.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Write a word-frequency scanner checking raw document files for terms</t>
+        </is>
+      </c>
+      <c r="G8" s="6">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/datastructures.html#dictionaries", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=daefaLgNkw0", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Python Functions Core</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>def statement parameters, return tracks, positional arguments, keyword unpacking (*args, **kwargs)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>To bundle messy code paths into cleanly organized, reusable functional building blocks.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Encapsulate loose collection code blocks into modular reusable functions</t>
+        </is>
+      </c>
+      <c r="G9" s="10">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/controlflow.html#defining-functions", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9Os0o3wXykM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Project: File Ingestion</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>File reading strings natively, context managers (with open), text string modifications, JSON parsing</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>To join native data structures, building functional file parsing scripts from scratch.</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Project: Code a CLI-driven Retail System saving records dynamically via context blocks</t>
+        </is>
+      </c>
+      <c r="G10" s="6">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/inputoutput.html#reading-and-writing-files", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Uh2ebFW8OYM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Day 29</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Python OOP: Classes</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Class blueprints instantiation, instance variables, methods, constructors (__init__), namespaces</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>To group structured methods and state variables into reusable object blueprints.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Model core corporate elements (e.g. Employee data card structures) using objects</t>
+        </is>
+      </c>
+      <c r="G11" s="10">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/classes.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZDa-Z5JzLYM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Day 30</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Python OOP: Inheritance</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Hierarchical inheritance, sub-classes expansion, function polymorphism, custom method overrides</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>To establish flexible, hierarchical system dependencies without code duplication.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Extend functional class layers into advanced sub-category objects overriding method calls</t>
+        </is>
+      </c>
+      <c r="G12" s="6">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/classes.html#inheritance", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H12" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RSl87lqOXDE", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Day 31</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Python OOP: Encapsulation</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Private attributes (__), property getters/setters, try-except-finally blocks, custom errors</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>To implement defensive exception containment rules protecting critical module data metrics.</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Enforce strict input verification masks using private properties and exception catch blocks</t>
+        </is>
+      </c>
+      <c r="G13" s="10">
+        <f>HYPERLINK("https://docs.python.org/3/tutorial/errors.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=apACNr7YdyE", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Day 32</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Core Library: NumPy Basics</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ND-arrays properties, vector types, initializing elements (zeros, ones, arange), slicing coordinates</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>To replace loop operations with high-speed vectorized computation blocks.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Initialize multi-dimensional arrays, slicing target internal matrix sub-regions</t>
+        </is>
+      </c>
+      <c r="G14" s="6">
+        <f>HYPERLINK("https://numpy.org/doc/stable/user/absolute_beginners.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H14" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Day 33</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Core Library: NumPy Vector</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Vector math rules, universal functions (ufuncs), axis aggregate statistics, shape transformations</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>To execute algebraic adjustments across extensive multi-axis grids instantly.</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Flatten complex multi-dimensional visual input channel blocks down to linear feature frames</t>
+        </is>
+      </c>
+      <c r="G15" s="10">
+        <f>HYPERLINK("https://numpy.org/doc/stable/reference/ufuncs.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H15" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Day 34</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Core Library: NumPy Masks</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Matrix broadcasting alignments, boolean masking logic filters, index arrays extraction</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>To filter numerical rows instantly using spatial boolean mask matrices.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Extract numerical vector values from record lines exceeding standard outliers via boolean filters</t>
+        </is>
+      </c>
+      <c r="G16" s="6">
+        <f>HYPERLINK("https://numpy.org/doc/stable/user/basics.broadcasting.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H16" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QUT1VHiHSmM", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Day 35</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Core Library: Pandas Data</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Series attributes, DataFrame layouts, ingestion connectors (read_csv, read_excel, read_json)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>To manage storage inputs as queryable tabular layers programmatically.</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Load coarse raw data frames, isolating target coordinate rows via boolean masks</t>
+        </is>
+      </c>
+      <c r="G17" s="10">
+        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/dsintro.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H17" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Day 36</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Core Library: Pandas Loc</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Explicit index locators (loc/iloc), compound query masks, sorting parameters labels</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>To isolate data partitions using exact coordinate axis labels safely.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Filter customer dataset rows matching multiple custom financial threshold ranges</t>
+        </is>
+      </c>
+      <c r="G18" s="6">
+        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/indexing.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H18" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Day 37</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Pandas: Data Cleaning</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Missing data tracks (isnull), data imputations via fillna, deleting observations (dropna)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>To handle missing data blocks cleanly using statistical column median rules.</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Construct an automated cleansing pipe replacing missing cells with column median values</t>
+        </is>
+      </c>
+      <c r="G19" s="10">
+        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/missing_data.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Day 38</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Pandas: Column Mapping</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Feature engineering, element-wise transformations (.apply), column splitting, mapping strings</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>To map continuous feature columns and extract components from unstructured categories.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Convert continuous transaction columns into categorized string feature groups dynamically</t>
+        </is>
+      </c>
+      <c r="G20" s="6">
+        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/basics.html#function-application", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Day 39</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Pandas: Aggregations</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Splitting segments via groupby, multi-aggregations (.agg), multi-key table lookups via merge</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>To connect separate transactional tables and group data points into segment metrics.</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Combine customer support interaction log frames with transactional record fields</t>
+        </is>
+      </c>
+      <c r="G21" s="10">
+        <f>HYPERLINK("https://pandas.pydata.org/docs/user_guide/groupby.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZyhVh-qRZPA", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Day 40</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Data Vis: Matplotlib Core</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Figure canvas layouts, axis properties formatting, titles, labels, legends customization, grids</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>To build polished graphical representations conveying key data features clearly.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Format active chart components using explicit font styles, legend bounds, and hex colors</t>
+        </is>
+      </c>
+      <c r="G22" s="6">
+        <f>HYPERLINK("https://matplotlib.org/stable/users/explain/quick_start.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H22" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Day 41</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Data Vis: Plots &amp; Bounds</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Histograms bins setups, box plots distributions, scatter plots with alpha transparency parameter settings</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>To spot statistical variations, spatial correlations, and outliers visually.</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Graph product distribution ranges to inspect feature data variations and catch outliers</t>
+        </is>
+      </c>
+      <c r="G23" s="10">
+        <f>HYPERLINK("https://matplotlib.org/stable/api/_as_gen/matplotlib.pyplot.hist.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Day 42</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Data Vis: Layout Grids</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Multi-panel subplots creation (plt.subplots), axis coordinates routing, exporting graphics (savefig)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>To bundle separate metrics into uniform scientific report layouts cleanly.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Construct unified multi-chart dashboard views showing lines, bars, and boxes side-by-side</t>
+        </is>
+      </c>
+      <c r="G24" s="6">
+        <f>HYPERLINK("https://matplotlib.org/stable/gallery/subplots_axes_and_figures/subplots_demo.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H24" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=wB9C0Mz9gSo", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Day 43</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Scikit-Learn Prep Rules</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Data split partitions (train_test_split), categorical encoding mappings, standard data scaling</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>To partition metrics arrays and scale independent features uniformly before running modeling.</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Pass unpolished string features through robust preprocessing pipelines utilizing automated scaling arrays</t>
+        </is>
+      </c>
+      <c r="G25" s="10">
+        <f>HYPERLINK("https://scikit-learn.org/stable/modules/preprocessing.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLblh5JKOoLUICTaGLRoHQDuF_7q2GfuJF", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Day 44</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Scikit-Learn Regression</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Supervised Ordinary Least Squares (LinearRegression), matching fit indices, checking model attributes</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>To compute continuous linear parameters and trace parameter correlation indicators.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Build and fit a predictive regression model tracking feature correlations to metric outputs</t>
+        </is>
+      </c>
+      <c r="G26" s="6">
+        <f>HYPERLINK("https://scikit-learn.org/stable/modules/linear_model.html#ordinary-least-squares", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H26" s="6">
+        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLblh5JKOoLUICTaGLRoHQDuF_7q2GfuJF", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Day 45</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Scikit-Learn Diagnostic</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Loss scoring calculators (mean_absolute_error, mean_squared_error, r2_score variance metric boundaries)</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>To verify model predictive drop thresholds against test subsets.</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Compute continuous validation errors testing models against separate check files</t>
+        </is>
+      </c>
+      <c r="G27" s="10">
+        <f>HYPERLINK("https://scikit-learn.org/stable/modules/model_evaluation.html#regression-metrics", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H27" s="10">
+        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLKnIA16_RmvbAl7lyqVvRI-cz3BwAd3mU", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Day 46</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Project: Pipeline Release</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Pipeline blocks assembly, grid parameter hyperparameter tuning loops via GridSearchCV arrays via Git</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>To build and track complete data-prep to model-inference flows via Git.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Project: Develop OOP Data Processing, Cleaning &amp; Visual Reporting Engine via Git Workflow</t>
+        </is>
+      </c>
+      <c r="G28" s="6">
+        <f>HYPERLINK("https://scikit-learn.org/stable/modules/generated/sklearn.pipeline.Pipeline.html", "Docs Portal")</f>
+        <v/>
+      </c>
+      <c r="H28" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0B5eIE_1vpU", "Watch Video")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2242,14 +2600,14 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Business Intelligence Visual Reports &amp; Analytical DAX Modeling (Days 40 - 46)</t>
+          <t>Business Intelligence Visual Reports &amp; Analytical DAX Modeling (Days 47 - 53)</t>
         </is>
       </c>
     </row>
@@ -2296,15 +2654,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Day 40</t>
+          <t>Day 47</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2336,15 +2694,15 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Day 41</t>
+          <t>Day 48</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2376,15 +2734,15 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Day 42</t>
+          <t>Day 49</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2416,15 +2774,15 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Day 43</t>
+          <t>Day 50</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2456,15 +2814,15 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Day 44</t>
+          <t>Day 51</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2496,15 +2854,15 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Day 45</t>
+          <t>Day 52</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2536,15 +2894,15 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Day 46</t>
+          <t>Day 53</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Week 7</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -2584,7 +2942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2600,13 +2958,13 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supervised Classifiers, Ensemble Estimators &amp; Unsupervised Clustering Modalities (Days 47 - 58)</t>
+          <t>Supervised Classifiers, Ensemble Estimators &amp; Unsupervised Clustering Modalities (Days 54 - 65)</t>
         </is>
       </c>
     </row>
@@ -2653,15 +3011,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Day 47</t>
+          <t>Day 54</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2693,15 +3051,15 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Day 48</t>
+          <t>Day 55</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2733,15 +3091,15 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Day 49</t>
+          <t>Day 56</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2773,15 +3131,15 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Day 50</t>
+          <t>Day 57</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2805,7 +3163,7 @@
         </is>
       </c>
       <c r="G7" s="10">
-        <f>HYPERLINK("https://scikit-learn.org/stable/modules/tree.html", "Official Docs")</f>
+        <f>HYPERLINK("https://scikit-learn.org/stable/tree.html", "Official Docs")</f>
         <v/>
       </c>
       <c r="H7" s="10">
@@ -2813,15 +3171,15 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Day 51</t>
+          <t>Day 58</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -2853,15 +3211,15 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Day 52</t>
+          <t>Day 59</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2893,15 +3251,15 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Day 53</t>
+          <t>Day 60</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 9</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2933,15 +3291,15 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Day 54</t>
+          <t>Day 61</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Week 10</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2973,15 +3331,15 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Day 55</t>
+          <t>Day 62</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Week 10</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3013,15 +3371,15 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Day 56</t>
+          <t>Day 63</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Week 10</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -3053,15 +3411,15 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Day 57</t>
+          <t>Day 64</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Week 10</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3071,7 +3429,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Covariance space projection parsing, principal axes vectors, explained variance tracking</t>
+          <t>Covariance space matrix parsing, component projections, tracking explained variances</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3093,15 +3451,15 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Day 58</t>
+          <t>Day 65</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Week 10</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -3141,7 +3499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3157,13 +3515,13 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reinforcement Learning Automations &amp; Tabular Q-Table Environments (Days 59 - 66)</t>
+          <t>Reinforcement Learning Automations &amp; Tabular Q-Table Environments (Days 66 - 73)</t>
         </is>
       </c>
     </row>
@@ -3210,15 +3568,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Day 59</t>
+          <t>Day 66</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3250,15 +3608,15 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Day 60</t>
+          <t>Day 67</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -3290,15 +3648,15 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Day 61</t>
+          <t>Day 68</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3330,15 +3688,15 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Day 62</t>
+          <t>Day 69</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -3370,15 +3728,15 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Day 63</t>
+          <t>Day 70</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3410,15 +3768,15 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Day 64</t>
+          <t>Day 71</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3450,15 +3808,15 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Day 65</t>
+          <t>Day 72</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3490,15 +3848,15 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Day 66</t>
+          <t>Day 73</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 11</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -3527,563 +3885,6 @@
       </c>
       <c r="H11" s="10">
         <f>HYPERLINK("https://www.youtube.com/playlist?list=PLQY2H8rRoyvzoUYIq_xoGZ6UduivK5w7r", "Watch Video Course")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Neural Networks, Computer Vision CNN Topologies, Sequential LSTMs &amp; PyTorch Core Algorithms (Days 67 - 78)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Thematic Architecture / Algorithm</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Mathematical Formulations &amp; Block Designs</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Purpose (Why Learn This Algorithm?)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>PyTorch Framework Step / Practical Lab</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Framework Reference Link</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>YouTube Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Day 67</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Foundations: Perceptrons &amp; MLPs</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Multi-Layer Perceptron (MLP), artificial dense nodes, weighted sums, forward propagation matrix math, linear constraints limits</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>To construct basic linear combination networks that form the core structural rows of deep networks.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Construct single logical perceptrons tracking weights manually via PyTorch tensors</t>
-        </is>
-      </c>
-      <c r="G4" s="6">
-        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/basics/intro.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H4" s="6">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Day 68</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Foundations: Activations &amp; Backprop</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Non-linear activations (ReLU, Sigmoid, Softmax equations), partial derivatives calculus, multivariable Chain Rule error mapping</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>To break linear alignment bottlenecks, calculating weight gradient deltas systematically backwards across network layers.</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Plot derivative gradients for common activations and trace automated tensor autograd steps</t>
-        </is>
-      </c>
-      <c r="G5" s="10">
-        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/blitz/autograd_tutorial.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H5" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VMj-3S1tku0", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Day 69</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Foundations: Loss &amp; Adam Optimizers</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cross-entropy loss metric formula, MSE functions, Adam optimizers (momentum tracking, dynamic adaptive step changes)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>To manage dynamic adjustment loops that update network weights based on running loss residues.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Write raw PyTorch optimization loops adjusting parameter matrices using custom criteria functions</t>
-        </is>
-      </c>
-      <c r="G6" s="6">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/optim.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H6" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Day 70</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Project: PyTorch Multi-Class Classifier</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Structuring nn.Module objects, forward pass methods, custom Dataset loader classes, mini-batch management (DataLoader)</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>To pack dense network blocks and mini-batch pipelines into scalable object models.</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>Project: Code and Train a Multi-Layer Perceptron using PyTorch over numeric tabular datasets</t>
-        </is>
-      </c>
-      <c r="G7" s="10">
-        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/basics/buildmodel_tutorial.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H7" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Day 71</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Computer Vision: Baseline CNNs</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2D Convolution operations, sliding matrix kernel filters, feature extraction grids, spatial channel mappings, stride and padding logic</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>To process digital vision matrices programmatically without stripping vital spatial pixel proximity features.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Manually compute visual grid feature maps passing across kernel filters using PyTorch blocks</t>
-        </is>
-      </c>
-      <c r="G8" s="6">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/generated/torch.nn.Conv2d.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Day 72</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Computer Vision: Max Pooling Networks</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Max pooling metrics, stride subsampling, feature contraction maps, stacking Conv-Pooling blocks hierarchically</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>To downsample feature maps, extracting key invariant metrics while cutting parameter counts to prevent overfit.</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Assemble a functional structural convolutional neural network (CNN) architecture inside nn.Module</t>
-        </is>
-      </c>
-      <c r="G9" s="10">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/nn.html#convolution-layers", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H9" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Day 73</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Computer Vision: ResNet Topologies</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Residual connection shortcut bypass routes, skip connections logic, deep network vanishing gradients mitigation</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>To bypass deep convolution nodes directly, curing vanishing gradients and enabling stable ultra-deep model training.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Build residual skip-connection code layers routing inputs directly around standard blocks</t>
-        </is>
-      </c>
-      <c r="G10" s="6">
-        <f>HYPERLINK("https://pytorch.org/vision/stable/models.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Day 74</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Project: Vision Transfer Learning</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Pretrained classification backbones loading, freezing feature layers weights, matching custom output target classification heads</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>To repurpose visual feature extractions learned from massive image datasets to achieve accurate custom tasks quickly.</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Project: Deploy Custom PyTorch ResNet Model on Color Image Datasets utilizing image transforms</t>
-        </is>
-      </c>
-      <c r="G11" s="10">
-        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/transfer_learning_tutorial.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Day 75</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Sequential Models: Word Embeddings</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Text parsing tokenization, continuous vocabulary indexes mapping, dense continuous vector spaces, Word2Vec continuous architectures</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>To project discrete strings into dense kontinuierliche coordinate spaces tracking semantic similarity scores.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Map vocabulary string tokens to continuous neural embeddings, calculating spatial cosine distances</t>
-        </is>
-      </c>
-      <c r="G12" s="6">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/generated/torch.nn.Embedding.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Day 76</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Sequential Models: Recurrent RNNs</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Recurrent Neural Networks (RNN) looping blocks, tracking rolling historical hidden states (h_t), sequential bottlenecks processing</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>To analyze variable time-series and token runs sequentially by feeding hidden state indices recursively.</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Build token character looping networks tracking historical hidden states in PyTorch</t>
-        </is>
-      </c>
-      <c r="G13" s="10">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/generated/torch.nn.RNN.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Day 77</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Sequential Models: LSTM Gated Systems</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Long Short-Term Memory (LSTM) cells layout, forget gate parameters math, input gate updates, output gating metrics, continuous cell context tracking</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>To manage context over long textual steps, using dedicated continuous gates to prevent sequence memory drop bounds.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Train PyTorch LSTM architectures on variable sequential time-series indicators smoothly</t>
-        </is>
-      </c>
-      <c r="G14" s="6">
-        <f>HYPERLINK("https://pytorch.org/docs/stable/generated/torch.nn.LSTM.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H14" s="6">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=AsN_g6wIbyA", "Watch Algorithm Course")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Day 78</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Project: Sequential Text Forecaster</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Bi-directional layer configurations, continuous embedding transformations, unpacking sequence runs matrices</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>To bundle recurrent gating networks into predictive files capable of forecasting narrative arrays.</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Project: Build Deep LSTM Network to Predict and Forecast Context Text Streams and timeline parameters</t>
-        </is>
-      </c>
-      <c r="G15" s="10">
-        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/nlp/sequence_models_tutorial.html", "Official Reference")</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
-        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
         <v/>
       </c>
     </row>
@@ -4101,6 +3902,443 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Neural Networks, Computer Vision CNN Topologies, Sequential LSTMs &amp; PyTorch Core Algorithms (Days 74 - 82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Thematic Architecture / Algorithm</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mathematical Formulations &amp; Block Designs</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Purpose (Why Learn This Algorithm?)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>PyTorch Framework Step / Practical Lab</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Framework Reference Link</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>YouTube Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day 74</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Foundations: Perceptrons &amp; MLPs</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Multi-Layer Perceptron (MLP), artificial dense nodes, weighted sums, forward propagation matrix math, linear constraints limits</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>To construct basic linear combination networks that form the core structural rows of deep networks.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Construct single logical perceptrons tracking weights manually via PyTorch tensors</t>
+        </is>
+      </c>
+      <c r="G4" s="6">
+        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/basics/intro.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Day 75</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Foundations: Activations &amp; Backprop</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non-linear activations (ReLU, Sigmoid, Softmax equations), partial derivatives calculus, multivariable Chain Rule error mapping</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>To break linear alignment bottlenecks, calculating weight gradient deltas systematically backwards across network layers.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Plot derivative gradients for common activations and trace automated tensor autograd steps</t>
+        </is>
+      </c>
+      <c r="G5" s="10">
+        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/blitz/autograd_tutorial.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VMj-3S1tku0", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Day 76</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Foundations: Loss &amp; Adam Optimizers</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Cross-entropy loss metric formula, MSE functions, Adam optimizers (momentum tracking, dynamic adaptive step changes)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>To manage dynamic adjustment loops that update network weights based on running loss residues.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Write raw PyTorch optimization loops adjusting parameter matrices using custom criteria functions</t>
+        </is>
+      </c>
+      <c r="G6" s="6">
+        <f>HYPERLINK("https://pytorch.org/docs/stable/optim.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Day 77</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Project: PyTorch Multi-Class Classifier</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Structuring nn.Module objects, forward pass methods, custom Dataset loader classes, mini-batch management (DataLoader)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>To pack dense network blocks and mini-batch pipelines into scalable object models.</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Project: Code and Train a Multi-Layer Perceptron using PyTorch over numeric tabular datasets</t>
+        </is>
+      </c>
+      <c r="G7" s="10">
+        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/basics/buildmodel_tutorial.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Day 78</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Computer Vision: Baseline CNNs</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2D Convolution operations, sliding matrix kernel filters, feature extraction grids, spatial channel mappings, stride and padding logic</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>To process digital vision matrices programmatically without stripping vital spatial pixel proximity features.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Manually compute visual grid feature maps passing across kernel filters using PyTorch blocks</t>
+        </is>
+      </c>
+      <c r="G8" s="6">
+        <f>HYPERLINK("https://pytorch.org/docs/stable/generated/torch.nn.Conv2d.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Day 79</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Computer Vision: Max Pooling Networks</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Max pooling metrics, stride subsampling, feature contraction maps, stacking Conv-Pooling blocks hierarchically</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>To downsample feature maps, extracting key invariant metrics while cutting parameter counts to prevent overfit.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Assemble a functional structural convolutional neural network (CNN) architecture inside nn.Module</t>
+        </is>
+      </c>
+      <c r="G9" s="10">
+        <f>HYPERLINK("https://pytorch.org/docs/stable/nn.html#convolution-layers", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Day 80</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Computer Vision: ResNet Topologies</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Residual connection shortcut bypass routes, skip connections logic, deep network vanishing gradients mitigation</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>To bypass deep convolution nodes directly, curing vanishing gradients and enabling stable ultra-deep model training.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Build residual skip-connection code layers routing inputs directly around standard blocks</t>
+        </is>
+      </c>
+      <c r="G10" s="6">
+        <f>HYPERLINK("https://pytorch.org/vision/stable/models.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Day 81</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Project: Vision Transfer Learning</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Pretrained classification backbones loading, freezing feature layers weights, matching custom output target classification heads</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>To repurpose visual feature extractions learned from massive image datasets to achieve accurate custom tasks quickly.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Project: Deploy Custom PyTorch ResNet Model on Color Image Datasets utilizing image transforms</t>
+        </is>
+      </c>
+      <c r="G11" s="10">
+        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/transfer_learning_tutorial.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=V_xro1bcAuA", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Day 82</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Project: Sequence Prediction</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Bi-directional layers, embedding layers, unpacking variable sequence runs</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>To construct sequential architectures forecasting narrative patterns.</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Project: Build Deep LSTM Network to Predict Context Text Streams</t>
+        </is>
+      </c>
+      <c r="G12" s="6">
+        <f>HYPERLINK("https://pytorch.org/tutorials/beginner/nlp/sequence_models_tutorial.html", "Official Reference")</f>
+        <v/>
+      </c>
+      <c r="H12" s="6">
+        <f>HYPERLINK("https://www.youtube.com/playlist?list=PLAqhIrjkxbuWI23v9cThsA9GvCAUhFf6o", "Watch Algorithm Course")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4110,14 +4348,14 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Generative AI Engineering, RAG Systems, API Services &amp; Container Deployments (Days 72 - 85)</t>
+          <t>Generative AI Engineering, RAG Systems, API Services &amp; Container Deployments (Days 83 - 96)</t>
         </is>
       </c>
     </row>
@@ -4164,15 +4402,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Day 72</t>
+          <t>Day 83</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 15</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4204,15 +4442,15 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Day 73</t>
+          <t>Day 84</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 15</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4244,15 +4482,15 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Day 74</t>
+          <t>Day 85</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 15</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4284,15 +4522,15 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Day 75</t>
+          <t>Day 86</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 15</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4324,15 +4562,15 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Day 76</t>
+          <t>Day 87</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 15</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -4364,15 +4602,15 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Day 77</t>
+          <t>Day 88</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Week 12</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4404,15 +4642,15 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Day 78</t>
+          <t>Day 89</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Week 12</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4444,15 +4682,15 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Day 79</t>
+          <t>Day 90</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Week 12</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4484,15 +4722,15 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Day 80</t>
+          <t>Day 91</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Week 12</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -4524,15 +4762,15 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Day 81</t>
+          <t>Day 92</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Week 12</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -4564,15 +4802,15 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Day 82</t>
+          <t>Day 93</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Week 17</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4604,15 +4842,15 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Day 83</t>
+          <t>Day 94</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Week 17</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4644,15 +4882,15 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Day 84</t>
+          <t>Day 95</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Week 17</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -4662,7 +4900,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Docker architectures, structural environment encapsulation, configuring base Dockerfile rules</t>
+          <t>Docker architectures, structural environment encapsulation, configuring base `Dockerfile` rules</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4684,15 +4922,15 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Day 85</t>
+          <t>Day 96</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Week 17</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
